--- a/broker_forms/009_insurance_binder_request_form--broker_forms.xlsx
+++ b/broker_forms/009_insurance_binder_request_form--broker_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>insurance_binder_request_form</t>
+          <t>policy_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>insurance_binder_request_form</t>
+          <t>Policy Type</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>policy_type</t>
+          <t>contract_start_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>policy_type</t>
+          <t>Contract Start Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>policy_number</t>
+          <t>contract_end_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>policy_number</t>
+          <t>Contract End Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contract_start_date</t>
+          <t>policy_start_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contract_start_date</t>
+          <t>Policy Start Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contract_end_date</t>
+          <t>policy_end_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contract_end_date</t>
+          <t>Policy End Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>policy_start_date</t>
+          <t>policy_period</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>policy_start_date</t>
+          <t>Policy Period</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>policy_end_date</t>
+          <t>contract_number</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>policy_end_date</t>
+          <t>Contract Number</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contract_date</t>
+          <t>policy_number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contract_date</t>
+          <t>Policy Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>policy_period</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>policy_period</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contract_period</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contract_period</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>contract_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>Contract Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contract_effective_date</t>
+          <t>policy_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contract_effective_date</t>
+          <t>Policy Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>coverage_start_date</t>
+          <t>effective_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>coverage_start_date</t>
+          <t>Effective Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>coverage_end_date</t>
+          <t>coverage_date</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>coverage_end_date</t>
+          <t>Coverage Date</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>policy_start_date</t>
+          <t>policy_period_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>policy_start_date</t>
+          <t>Policy Period 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>policy_end_date</t>
+          <t>contract_period</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>policy_end_date</t>
+          <t>Contract Period</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contract_start_date</t>
+          <t>policy_contract_date</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>contract_start_date</t>
+          <t>Policy Contract Date</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contract_end_date</t>
+          <t>coverage_policy_date</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>contract_end_date</t>
+          <t>Coverage Policy Date</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>policy_date</t>
+          <t>contract_coverage_date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>policy_date</t>
+          <t>Contract Coverage Date</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>coverage_date</t>
+          <t>policy_effective_date</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>coverage_date</t>
+          <t>Policy Effective Date</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>contract_coverage_date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>contract_coverage_date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contract_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>contract_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>policy_contract_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>policy_contract_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>coverage_policy_date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>coverage_policy_date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>policy_effective_date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>policy_effective_date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>policy_type</t>
+          <t>policy_type_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Policy Type</t>
+          <t>Policy Type 1</t>
         </is>
       </c>
     </row>
